--- a/output/brahmi_pearls_x.xlsx
+++ b/output/brahmi_pearls_x.xlsx
@@ -625,7 +625,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "stress relief supplements", "landing_page_type": "product_detail", "match_intent_core": "stress_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "causes", "jobs", "yoga", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_relief_medicine", "product_format": "unknown", "product_variant": null, "query_shape": "product_only", "risk_flags": {"ambiguous_product_mapping": true, "competitor_term_present": false, "disease_term_present": false, "medical_claim_sensitive": true}}</t>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "condition", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "stress relief tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_relief", "negative_keyword_needs": ["free", "home remedy", "remedies", "symptoms", "causes", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "high", "product_family": "stress_relief_supplement", "product_format": "other", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": true, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "stress relief supplements", "landing_page_type": "product_detail", "match_intent_core": "stress_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "causes", "jobs", "yoga", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_relief_medicine", "product_format": "tablet", "product_variant": null, "query_shape": "product_only", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": false, "medical_claim_sensitive": true}}</t>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "condition", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "stress relief tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_relief", "negative_keyword_needs": ["free", "home remedy", "remedies", "symptoms", "causes", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "high", "product_family": "stress_relief_supplement", "product_format": "other", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": true, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,12 +724,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>stress relief pills</t>
+          <t>tension relief medicine</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "stress relief supplements", "landing_page_type": "product_detail", "match_intent_core": "stress_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "causes", "jobs", "yoga", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_relief_medicine", "product_format": "tablet", "product_variant": null, "query_shape": "product_only", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": false, "medical_claim_sensitive": true}}</t>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "condition", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "stress relief tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_relief", "negative_keyword_needs": ["free", "home remedy", "remedies", "symptoms", "causes", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "high", "product_family": "stress_relief_supplement", "product_format": "other", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": true, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>stress relief pills</t>
+          <t>tension relief medicine</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -776,12 +776,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>stress reliever supplement</t>
+          <t>stress relief tablet</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "stress relief supplements", "landing_page_type": "product_detail", "match_intent_core": "stress_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "causes", "jobs", "yoga", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_relief_supplement", "product_format": "other", "product_variant": null, "query_shape": "product_only", "risk_flags": {"ambiguous_product_mapping": true, "competitor_term_present": false, "disease_term_present": false, "medical_claim_sensitive": true}}</t>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "condition", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "stress relief tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_relief", "negative_keyword_needs": ["free", "home remedy", "remedies", "symptoms", "causes", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "high", "product_family": "stress_relief_supplement", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>stress reliever supplement</t>
+          <t>stress relief tablet</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -828,12 +828,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>best stress relief medicine</t>
+          <t>stress relief pills</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "best", "condition_or_need": "stress", "english_equivalent": "stress relief supplements", "landing_page_type": "product_detail", "match_intent_core": "stress_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "causes", "cheap", "jobs", "yoga"], "original_language": "normalized", "phrase_match_expansion_risk": "high", "product_family": "stress_relief_medicine", "product_format": "unknown", "product_variant": null, "query_shape": "product_only", "risk_flags": {"ambiguous_product_mapping": true, "competitor_term_present": false, "disease_term_present": false, "medical_claim_sensitive": true}}</t>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "condition", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "stress relief tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_relief", "negative_keyword_needs": ["free", "home remedy", "remedies", "symptoms", "causes", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "high", "product_family": "stress_relief_supplement", "product_format": "other", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": true, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -858,17 +858,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>evaluation_search_brahmi_pearls_x</t>
+          <t>condition_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Evaluation/comparison style query; routed to evaluation_search_brahmi_pearls_x (Commercial, MOF).</t>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF).</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>best stress relief medicine</t>
+          <t>stress relief pills</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -880,12 +880,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>anxiety and stress relief pills</t>
+          <t>stress tablets</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress_and_anxiety", "english_equivalent": "stress and anxiety relief supplements", "landing_page_type": "product_detail", "match_intent_core": "anxiety_and_stress_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "causes", "therapy", "yoga", "jobs", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_relief_medicine", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "condition", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "stress relief tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_relief", "negative_keyword_needs": ["free", "home remedy", "remedies", "symptoms", "causes", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "high", "product_family": "stress_relief_supplement", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>anxiety and stress relief pills</t>
+          <t>stress tablets</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -932,12 +932,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>stress and anxiety relief pills</t>
+          <t>anxiety and stress tablets</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress_and_anxiety", "english_equivalent": "stress and anxiety relief supplements", "landing_page_type": "product_detail", "match_intent_core": "anxiety_and_stress_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "causes", "therapy", "yoga", "jobs", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_relief_medicine", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "condition", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "anxiety_and_stress", "english_equivalent": "anxiety and stress relief tablets", "landing_page_type": "product_detail", "match_intent_core": "anxiety_and_stress_relief", "negative_keyword_needs": ["free", "home remedy", "remedies", "symptoms", "causes", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "high", "product_family": "stress_relief_supplement", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>stress and anxiety relief pills</t>
+          <t>anxiety and stress tablets</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -984,12 +984,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>anxiety stress relief pills</t>
+          <t>stress free tablets</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress_and_anxiety", "english_equivalent": "stress and anxiety relief supplements", "landing_page_type": "product_detail", "match_intent_core": "anxiety_and_stress_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "causes", "therapy", "yoga", "jobs", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_relief_medicine", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "condition", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "stress relief tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_relief", "negative_keyword_needs": ["free", "home remedy", "remedies", "symptoms", "causes", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "high", "product_family": "stress_relief_supplement", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>anxiety stress relief pills</t>
+          <t>stress free tablets</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1036,12 +1036,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>stress release pills</t>
+          <t>anxiety stress tablets</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "stress relief supplements", "landing_page_type": "product_detail", "match_intent_core": "stress_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "causes", "jobs", "yoga", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_relief_medicine", "product_format": "tablet", "product_variant": null, "query_shape": "product_only", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": false, "medical_claim_sensitive": true}}</t>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "condition", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "anxiety_and_stress", "english_equivalent": "anxiety and stress relief tablets", "landing_page_type": "product_detail", "match_intent_core": "anxiety_and_stress_relief", "negative_keyword_needs": ["free", "home remedy", "remedies", "symptoms", "causes", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "high", "product_family": "stress_relief_supplement", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>stress release pills</t>
+          <t>anxiety stress tablets</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1088,12 +1088,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>stress control pills</t>
+          <t>stress reliever supplement</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "stress relief supplements", "landing_page_type": "product_detail", "match_intent_core": "stress_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "causes", "jobs", "yoga", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_relief_medicine", "product_format": "tablet", "product_variant": null, "query_shape": "product_only", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": false, "medical_claim_sensitive": true}}</t>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "condition", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "stress relief tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_relief", "negative_keyword_needs": ["free", "home remedy", "remedies", "symptoms", "causes", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "high", "product_family": "stress_relief_supplement", "product_format": "other", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": true, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>stress control pills</t>
+          <t>stress reliever supplement</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1140,12 +1140,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>stress and anxiety relief supplements</t>
+          <t>himalaya stress relief tablet</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{"ad_copy_angle": "education", "ad_group_intent": "condition", "audience": null, "brand_scope": "generic", "commercial_intent": "informational", "condition_or_need": "stress_anxiety", "english_equivalent": "stress and anxiety relief supplements", "landing_page_type": "category", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "jobs", "career"], "original_language": "normalized", "phrase_match_expansion_risk": "high", "product_family": "stress_anxiety_relief_supplement", "product_format": "unknown", "product_variant": null, "query_shape": "condition_solution", "risk_flags": {"ambiguous_product_mapping": true, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+          <t>{"ad_copy_angle": "comparison", "ad_group_intent": "competitor", "audience": null, "brand_scope": "competitor", "commercial_intent": "buy", "condition_or_need": "stress_and_anxiety", "english_equivalent": "himalaya stress relief tablet", "landing_page_type": "comparison_page", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "jobs", "how to", "symptoms", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "high", "product_family": "stress_anxiety_relief", "product_format": "tablet", "product_variant": null, "query_shape": "competitor_product", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": true, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1170,17 +1170,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>condition_search_brahmi_pearls_x</t>
+          <t>competitor_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF).</t>
+          <t>Classified as Commercial at MOF; routed to competitor_search_brahmi_pearls_x.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>stress and anxiety relief supplements</t>
+          <t>himalaya stress relief tablet</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1192,12 +1192,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>anxiety stress relief supplement</t>
+          <t>best stress relief medicine</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{"ad_copy_angle": "education", "ad_group_intent": "condition", "audience": null, "brand_scope": "generic", "commercial_intent": "informational", "condition_or_need": "stress_anxiety", "english_equivalent": "stress and anxiety relief supplements", "landing_page_type": "category", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "jobs", "career"], "original_language": "normalized", "phrase_match_expansion_risk": "high", "product_family": "stress_anxiety_relief_supplement", "product_format": "unknown", "product_variant": null, "query_shape": "condition_solution", "risk_flags": {"ambiguous_product_mapping": true, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+          <t>{"ad_copy_angle": "review_social_proof", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "best", "condition_or_need": "stress_and_anxiety", "english_equivalent": "best stress relief tablets", "landing_page_type": "comparison_page", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "side effects", "jobs", "how to"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_anxiety_relief", "product_format": "unknown", "product_variant": null, "query_shape": "commercial_modifier", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1222,17 +1222,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>condition_search_brahmi_pearls_x</t>
+          <t>evaluation_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF).</t>
+          <t>Evaluation/comparison style query; routed to evaluation_search_brahmi_pearls_x (Commercial, MOF).</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>anxiety stress relief supplement</t>
+          <t>best stress relief medicine</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1244,12 +1244,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>stress anxiety relief supplements</t>
+          <t>tension relief tablets</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{"ad_copy_angle": "education", "ad_group_intent": "condition", "audience": null, "brand_scope": "generic", "commercial_intent": "informational", "condition_or_need": "stress_anxiety", "english_equivalent": "stress and anxiety relief supplements", "landing_page_type": "category", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "jobs", "career"], "original_language": "normalized", "phrase_match_expansion_risk": "high", "product_family": "stress_anxiety_relief_supplement", "product_format": "unknown", "product_variant": null, "query_shape": "condition_solution", "risk_flags": {"ambiguous_product_mapping": true, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress_and_anxiety", "english_equivalent": "tension relief tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "side effects", "jobs", "himalaya", "patanjali", "patent", "how to"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_anxiety_relief", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>stress anxiety relief supplements</t>
+          <t>tension relief tablets</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1296,12 +1296,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>stress away pills</t>
+          <t>stress reducing tablets</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{"ad_copy_angle": "education", "ad_group_intent": "condition", "audience": null, "brand_scope": "generic", "commercial_intent": "informational", "condition_or_need": "stress_anxiety", "english_equivalent": "stress and anxiety relief supplements", "landing_page_type": "category", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "jobs", "career"], "original_language": "normalized", "phrase_match_expansion_risk": "high", "product_family": "stress_anxiety_relief_supplement", "product_format": "unknown", "product_variant": null, "query_shape": "condition_solution", "risk_flags": {"ambiguous_product_mapping": true, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress_and_anxiety", "english_equivalent": "tension relief tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "side effects", "jobs", "himalaya", "patanjali", "patent", "how to"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_anxiety_relief", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>stress away pills</t>
+          <t>stress reducing tablets</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1348,12 +1348,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>sleeping pills for stress relief</t>
+          <t>anxiety and stress relief pills</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{"ad_copy_angle": "education", "ad_group_intent": "condition", "audience": null, "brand_scope": "generic", "commercial_intent": "informational", "condition_or_need": "stress_anxiety", "english_equivalent": "stress and anxiety relief supplements", "landing_page_type": "category", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "jobs", "career"], "original_language": "normalized", "phrase_match_expansion_risk": "high", "product_family": "stress_anxiety_relief_supplement", "product_format": "unknown", "product_variant": null, "query_shape": "condition_solution", "risk_flags": {"ambiguous_product_mapping": true, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress_and_anxiety", "english_equivalent": "tension relief tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "side effects", "jobs", "himalaya", "patanjali", "patent", "how to"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_anxiety_relief", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>sleeping pills for stress relief</t>
+          <t>anxiety and stress relief pills</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1400,12 +1400,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ayurvedic stress relief medicine</t>
+          <t>anxiety and stress relief tablets</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "condition", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress_anxiety", "english_equivalent": "ayurvedic stress relief medicine", "landing_page_type": "category", "match_intent_core": "ayurvedic_stress_relief_medicine", "negative_keyword_needs": ["free", "home remedy"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "ayurvedic_medicine", "product_format": "other", "product_variant": null, "query_shape": "condition_solution", "risk_flags": {"ambiguous_product_mapping": true, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress_and_anxiety", "english_equivalent": "tension relief tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "side effects", "jobs", "himalaya", "patanjali", "patent", "how to"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_anxiety_relief", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>ayurvedic stress relief medicine</t>
+          <t>anxiety and stress relief tablets</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1452,12 +1452,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>stress relief medicine in ayurveda</t>
+          <t>stress and anxiety relief pills</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "condition", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress_anxiety", "english_equivalent": "ayurvedic stress relief medicine", "landing_page_type": "category", "match_intent_core": "ayurvedic_stress_relief_medicine", "negative_keyword_needs": ["free", "home remedy"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "ayurvedic_medicine", "product_format": "other", "product_variant": null, "query_shape": "condition_solution", "risk_flags": {"ambiguous_product_mapping": true, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress_and_anxiety", "english_equivalent": "tension relief tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "side effects", "jobs", "himalaya", "patanjali", "patent", "how to"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_anxiety_relief", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1492,7 +1492,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>stress relief medicine in ayurveda</t>
+          <t>stress and anxiety relief pills</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1504,12 +1504,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>brahmi pearls</t>
+          <t>anxiety stress relief pills</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{"ad_copy_angle": "buy_now", "ad_group_intent": "brand_product", "audience": null, "brand_scope": "brand", "commercial_intent": "buy", "condition_or_need": null, "english_equivalent": "brahmi pearls kerala ayurveda", "landing_page_type": "product_detail", "match_intent_core": "brahmi_pearls", "negative_keyword_needs": ["free", "home remedy", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "low", "product_family": "brahmi_pearls", "product_format": "capsule", "product_variant": null, "query_shape": "brand_product", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": false, "medical_claim_sensitive": false}}</t>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress_and_anxiety", "english_equivalent": "tension relief tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "side effects", "jobs", "himalaya", "patanjali", "patent", "how to"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_anxiety_relief", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1524,27 +1524,27 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Navigational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>BOF</t>
+          <t>MOF</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>competitor_search_brahmi_pearls_x</t>
+          <t>condition_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Competitor + product query kept positive; routed to competitor_search_brahmi_pearls_x (Navigational, BOF).</t>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF).</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>brahmi pearls</t>
+          <t>anxiety stress relief pills</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1556,12 +1556,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>kerala ayurveda brahmi pearls</t>
+          <t>stress release tablets</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{"ad_copy_angle": "buy_now", "ad_group_intent": "brand_product", "audience": null, "brand_scope": "brand", "commercial_intent": "buy", "condition_or_need": null, "english_equivalent": "brahmi pearls kerala ayurveda", "landing_page_type": "product_detail", "match_intent_core": "brahmi_pearls", "negative_keyword_needs": ["free", "home remedy", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "low", "product_family": "brahmi_pearls", "product_format": "capsule", "product_variant": null, "query_shape": "brand_product", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": false, "medical_claim_sensitive": false}}</t>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress_and_anxiety", "english_equivalent": "tension relief tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "side effects", "jobs", "himalaya", "patanjali", "patent", "how to"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_anxiety_relief", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1576,27 +1576,27 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Navigational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>BOF</t>
+          <t>MOF</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>competitor_search_brahmi_pearls_x</t>
+          <t>condition_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Competitor + product query kept positive; routed to competitor_search_brahmi_pearls_x (Navigational, BOF).</t>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF).</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>kerala ayurveda brahmi pearls</t>
+          <t>stress release tablets</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1608,12 +1608,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>brahmi pearls kerala ayurveda</t>
+          <t>stress release pills</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{"ad_copy_angle": "buy_now", "ad_group_intent": "brand_product", "audience": null, "brand_scope": "brand", "commercial_intent": "buy", "condition_or_need": null, "english_equivalent": "brahmi pearls kerala ayurveda", "landing_page_type": "product_detail", "match_intent_core": "brahmi_pearls", "negative_keyword_needs": ["free", "home remedy", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "low", "product_family": "brahmi_pearls", "product_format": "capsule", "product_variant": null, "query_shape": "brand_product", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": false, "medical_claim_sensitive": false}}</t>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress_and_anxiety", "english_equivalent": "tension relief tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "side effects", "jobs", "himalaya", "patanjali", "patent", "how to"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_anxiety_relief", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1628,27 +1628,27 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Navigational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>BOF</t>
+          <t>MOF</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>competitor_search_brahmi_pearls_x</t>
+          <t>condition_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Competitor + product query kept positive; routed to competitor_search_brahmi_pearls_x (Navigational, BOF).</t>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF).</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>brahmi pearls kerala ayurveda</t>
+          <t>stress release pills</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1660,18 +1660,22 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>tension relief medicine</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
+          <t>stress control pills</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress_and_anxiety", "english_equivalent": "stress control tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "jobs"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_relief_supplement", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Negative Match</t>
+          <t>Phrase Match</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1686,32 +1690,44 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>negative_keywords</t>
+          <t>condition_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Ambiguous/off-primary-use-case intent</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF).</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>stress control pills</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>stress relief tablet</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
+          <t>stress relieving tablets</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress_and_anxiety", "english_equivalent": "stress control tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "jobs"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_relief_supplement", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Negative Match</t>
+          <t>Phrase Match</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1726,32 +1742,44 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>negative_keywords</t>
+          <t>condition_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF).</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>stress relieving tablets</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>stress tablets</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
+          <t>mental stress relief tablets</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress_and_anxiety", "english_equivalent": "stress control tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "jobs"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_relief_supplement", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Negative Match</t>
+          <t>Phrase Match</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1766,32 +1794,44 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>negative_keywords</t>
+          <t>condition_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF).</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>mental stress relief tablets</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>anxiety and stress tablets</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
+          <t>stress control tablets</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress_and_anxiety", "english_equivalent": "stress control tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "jobs"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_relief_supplement", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Negative Match</t>
+          <t>Phrase Match</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1806,32 +1846,44 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>negative_keywords</t>
+          <t>condition_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF).</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>stress control tablets</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>stress free tablets</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
+          <t>stress and anxiety relief supplements</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress_and_anxiety", "english_equivalent": "stress and anxiety relief supplements", "landing_page_type": "product_detail", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "jobs"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_relief_supplement", "product_format": "other", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Negative Match</t>
+          <t>Phrase Match</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1846,32 +1898,44 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>negative_keywords</t>
+          <t>condition_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF).</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>stress and anxiety relief supplements</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>anxiety stress tablets</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
+          <t>anxiety stress relief supplement</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress_and_anxiety", "english_equivalent": "stress and anxiety relief supplements", "landing_page_type": "product_detail", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "jobs"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_relief_supplement", "product_format": "other", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Negative Match</t>
+          <t>Phrase Match</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1886,32 +1950,44 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>negative_keywords</t>
+          <t>condition_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF).</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>anxiety stress relief supplement</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>himalaya stress relief tablet</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
+          <t>stress anxiety relief supplements</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress_and_anxiety", "english_equivalent": "stress and anxiety relief supplements", "landing_page_type": "product_detail", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "jobs"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_relief_supplement", "product_format": "other", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Negative Match</t>
+          <t>Phrase Match</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1926,32 +2002,44 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>negative_keywords</t>
+          <t>condition_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF).</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>stress anxiety relief supplements</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>tension relief tablets</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
+          <t>stress away pills</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress_and_anxiety", "english_equivalent": "stress control tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "jobs"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_relief_supplement", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Negative Match</t>
+          <t>Phrase Match</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1966,32 +2054,44 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>negative_keywords</t>
+          <t>condition_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF).</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>stress away pills</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>stress reducing tablets</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
+          <t>himalaya stress tablets</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "comparison", "ad_group_intent": "competitor", "audience": null, "brand_scope": "competitor", "commercial_intent": "buy", "condition_or_need": "stress_and_anxiety", "english_equivalent": "himalaya stress tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "jobs"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_relief_supplement", "product_format": "tablet", "product_variant": null, "query_shape": "brand_product", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": true, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Negative Match</t>
+          <t>Phrase Match</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2006,32 +2106,44 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>negative_keywords</t>
+          <t>competitor_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>Classified as Commercial at MOF; routed to competitor_search_brahmi_pearls_x.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>himalaya stress tablets</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>anxiety and stress relief tablets</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
+          <t>mind stress relief tablets</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress_and_anxiety", "english_equivalent": "stress control tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "jobs"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_relief_supplement", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Negative Match</t>
+          <t>Phrase Match</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2046,32 +2158,44 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>negative_keywords</t>
+          <t>condition_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF).</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>mind stress relief tablets</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>stress release tablets</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
+          <t>mental stress tablets</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "mental stress relief tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_relief_tablet", "negative_keyword_needs": ["free", "home remedy", "home remedies", "prescription"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "ayurvedic_stress_relief_medicine", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Negative Match</t>
+          <t>Phrase Match</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2086,32 +2210,44 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>negative_keywords</t>
+          <t>condition_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF).</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>mental stress tablets</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>stress relieving tablets</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
+          <t>stress management tablets</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "mental stress relief tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_relief_tablet", "negative_keyword_needs": ["free", "home remedy", "home remedies", "prescription"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "ayurvedic_stress_relief_medicine", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Negative Match</t>
+          <t>Phrase Match</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2126,32 +2262,44 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>negative_keywords</t>
+          <t>condition_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF).</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>stress management tablets</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>mental stress relief tablets</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
+          <t>stress relief ayurvedic tablets</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "mental stress relief tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_relief_tablet", "negative_keyword_needs": ["free", "home remedy", "home remedies", "prescription"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "ayurvedic_stress_relief_medicine", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Negative Match</t>
+          <t>Phrase Match</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2166,32 +2314,44 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>negative_keywords</t>
+          <t>condition_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF).</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>stress relief ayurvedic tablets</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>stress control tablets</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
+          <t>stress relief tablets in ayurveda</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "mental stress relief tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_relief_tablet", "negative_keyword_needs": ["free", "home remedy", "home remedies", "prescription"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "ayurvedic_stress_relief_medicine", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Negative Match</t>
+          <t>Phrase Match</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2206,32 +2366,44 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>negative_keywords</t>
+          <t>condition_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF).</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>stress relief tablets in ayurveda</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>himalaya stress tablets</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
+          <t>best stress relief tablets</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "comparison", "ad_group_intent": "evaluation", "audience": null, "brand_scope": "generic", "commercial_intent": "best", "condition_or_need": "stress", "english_equivalent": "best stress relief tablets", "landing_page_type": "comparison_page", "match_intent_core": "stress_relief_tablet", "negative_keyword_needs": ["free", "home remedy", "home remedies", "prescription"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "ayurvedic_stress_relief_medicine", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Negative Match</t>
+          <t>Phrase Match</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2246,32 +2418,44 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>negative_keywords</t>
+          <t>evaluation_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+          <t>Evaluation/comparison style query; routed to evaluation_search_brahmi_pearls_x (Commercial, MOF).</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>best stress relief tablets</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>mind stress relief tablets</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
+          <t>sleeping pills for stress relief</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "education", "ad_group_intent": "informational", "audience": null, "brand_scope": "generic", "commercial_intent": "informational", "condition_or_need": "stress", "english_equivalent": "sleeping pills for stress relief", "landing_page_type": "educational_page", "match_intent_core": "sleeping_pills_for_stress_relief", "negative_keyword_needs": ["prescription", "psychiatrist", "psychologist", "free"], "original_language": "normalized", "phrase_match_expansion_risk": "high", "product_family": "sleep_aids", "product_format": "tablet", "product_variant": null, "query_shape": "condition_solution", "risk_flags": {"ambiguous_product_mapping": true, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Negative Match</t>
+          <t>Phrase Match</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2286,72 +2470,96 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>negative_keywords</t>
+          <t>condition_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF).</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>sleeping pills for stress relief</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>stress aid tablets uses</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
+          <t>stress buster tablet</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "mental stress relief tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_relief_tablet", "negative_keyword_needs": ["free", "home remedy", "home remedies", "prescription"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "ayurvedic_stress_relief_medicine", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Negative Match</t>
+          <t>Broad Match</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>TOF</t>
+          <t>MOF</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>negative_keywords</t>
+          <t>product_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+          <t>Direct product-intent query; routed to product_search_brahmi_pearls_x (Commercial, MOF).</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>stress buster tablet</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>mental stress tablets</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
+          <t>stress reliever tablet</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "mental stress relief tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_relief_tablet", "negative_keyword_needs": ["free", "home remedy", "home remedies", "prescription"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "ayurvedic_stress_relief_medicine", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Negative Match</t>
+          <t>Broad Match</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2366,32 +2574,44 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>negative_keywords</t>
+          <t>product_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
+          <t>Direct product-intent query; routed to product_search_brahmi_pearls_x (Commercial, MOF).</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>stress reliever tablet</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>stress management tablets</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
+          <t>tablet for tension relief</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "mental stress relief tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_relief_tablet", "negative_keyword_needs": ["free", "home remedy", "home remedies", "prescription"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "ayurvedic_stress_relief_medicine", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Negative Match</t>
+          <t>Phrase Match</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2406,32 +2626,44 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>negative_keywords</t>
+          <t>condition_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF).</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>tablet for tension relief</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>stress relief ayurvedic tablets</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
+          <t>ayurvedic stress relief medicine</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "ayurvedic stress relief medicine", "landing_page_type": "product_detail", "match_intent_core": "ayurvedic_stress_relief_medicine", "negative_keyword_needs": ["free", "home remedy", "home remedies", "prescription"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "ayurvedic_stress_relief_medicine", "product_format": "unknown", "product_variant": null, "query_shape": "product_only", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Negative Match</t>
+          <t>Phrase Match</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2446,32 +2678,44 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>negative_keywords</t>
+          <t>condition_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF).</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ayurvedic stress relief medicine</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>stress relief tablets in ayurveda</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
+          <t>stress free tablets ayurvedic</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "condition", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "ayurvedic stress relief tablets", "landing_page_type": "condition_page", "match_intent_core": "stress_relief", "negative_keyword_needs": ["home remedy", "free", "symptoms", "causes"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "ayurvedic_stress_medicine", "product_format": "tablet", "product_variant": null, "query_shape": "condition_solution", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Negative Match</t>
+          <t>Phrase Match</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2486,32 +2730,44 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>negative_keywords</t>
+          <t>condition_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF).</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>stress free tablets ayurvedic</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>best stress relief tablets</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
+          <t>stress relief medicine in ayurveda</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "condition", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "ayurvedic stress relief tablets", "landing_page_type": "condition_page", "match_intent_core": "stress_relief", "negative_keyword_needs": ["home remedy", "free", "symptoms", "causes"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "ayurvedic_stress_medicine", "product_format": "tablet", "product_variant": null, "query_shape": "condition_solution", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Negative Match</t>
+          <t>Phrase Match</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2526,32 +2782,44 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>negative_keywords</t>
+          <t>condition_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF).</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>stress relief medicine in ayurveda</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>stress buster tablet</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
+          <t>ayurvedic stress tablets</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "condition", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "ayurvedic stress relief tablets", "landing_page_type": "condition_page", "match_intent_core": "stress_relief", "negative_keyword_needs": ["home remedy", "free", "symptoms", "causes"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "ayurvedic_stress_medicine", "product_format": "tablet", "product_variant": null, "query_shape": "condition_solution", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Negative Match</t>
+          <t>Phrase Match</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2566,72 +2834,96 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>negative_keywords</t>
+          <t>condition_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF).</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ayurvedic stress tablets</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>stress free tablets uses</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
+          <t>stress tablets ayurvedic</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "condition", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "ayurvedic stress relief tablets", "landing_page_type": "condition_page", "match_intent_core": "stress_relief", "negative_keyword_needs": ["home remedy", "free", "symptoms", "causes"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "ayurvedic_stress_medicine", "product_format": "tablet", "product_variant": null, "query_shape": "condition_solution", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Negative Match</t>
+          <t>Phrase Match</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>TOF</t>
+          <t>MOF</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>negative_keywords</t>
+          <t>condition_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF).</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>stress tablets ayurvedic</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>stress reliever tablet</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
+          <t>brahmi pearls</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": null, "english_equivalent": "brahmi pearls", "landing_page_type": "product_detail", "match_intent_core": "brahmi_pearls", "negative_keyword_needs": ["tablet", "free", "home remedy"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "brahmi", "product_format": "capsule", "product_variant": null, "query_shape": "product_only", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": false, "medical_claim_sensitive": false}}</t>
+        </is>
+      </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Negative Match</t>
+          <t>Phrase Match</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2646,32 +2938,44 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>negative_keywords</t>
+          <t>competitor_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+          <t>Competitor + product query kept positive; routed to competitor_search_brahmi_pearls_x (Commercial, MOF).</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>brahmi pearls</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>tablet for tension relief</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
+          <t>brahmi tablet</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": null, "english_equivalent": "brahmi tablets", "landing_page_type": "product_detail", "match_intent_core": "brahmi_tablet", "negative_keyword_needs": ["pearls", "capsule", "free", "home remedy"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "brahmi", "product_format": "tablet", "product_variant": null, "query_shape": "product_only", "risk_flags": {"ambiguous_product_mapping": true, "competitor_term_present": false, "disease_term_present": false, "medical_claim_sensitive": false}}</t>
+        </is>
+      </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Negative Match</t>
+          <t>Phrase Match</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2686,141 +2990,185 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>negative_keywords</t>
+          <t>competitor_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
+          <t>Competitor + product query kept positive; routed to competitor_search_brahmi_pearls_x (Commercial, MOF).</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>brahmi tablet</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>stress free tablets ayurvedic</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
+          <t>kerala ayurveda brahmi pearls</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "brand_trust", "ad_group_intent": "brand_product", "audience": null, "brand_scope": "brand", "commercial_intent": "buy", "condition_or_need": null, "english_equivalent": "brahmi pearls kerala ayurveda", "landing_page_type": "product_detail", "match_intent_core": "brahmi_pearls", "negative_keyword_needs": ["tablet", "home remedy", "free"], "original_language": "normalized", "phrase_match_expansion_risk": "low", "product_family": "brahmi", "product_format": "capsule", "product_variant": null, "query_shape": "brand_product", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": false, "medical_claim_sensitive": false}}</t>
+        </is>
+      </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Negative Match</t>
+          <t>Phrase Match</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Navigational</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>MOF</t>
+          <t>BOF</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>negative_keywords</t>
+          <t>competitor_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+          <t>Competitor + product query kept positive; routed to competitor_search_brahmi_pearls_x (Navigational, BOF).</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>kerala ayurveda brahmi pearls</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ayurvedic stress tablets</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
+          <t>brahmi pearls kerala ayurveda</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "brand_trust", "ad_group_intent": "brand_product", "audience": null, "brand_scope": "brand", "commercial_intent": "buy", "condition_or_need": null, "english_equivalent": "brahmi pearls kerala ayurveda", "landing_page_type": "product_detail", "match_intent_core": "brahmi_pearls", "negative_keyword_needs": ["tablet", "home remedy", "free"], "original_language": "normalized", "phrase_match_expansion_risk": "low", "product_family": "brahmi", "product_format": "capsule", "product_variant": null, "query_shape": "brand_product", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": false, "medical_claim_sensitive": false}}</t>
+        </is>
+      </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Negative Match</t>
+          <t>Phrase Match</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Navigational</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>MOF</t>
+          <t>BOF</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>negative_keywords</t>
+          <t>competitor_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
+          <t>Competitor + product query kept positive; routed to competitor_search_brahmi_pearls_x (Navigational, BOF).</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>brahmi pearls kerala ayurveda</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>stress tablets ayurvedic</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
+          <t>brahmi tablet kerala ayurveda</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "brand_trust", "ad_group_intent": "brand_product", "audience": null, "brand_scope": "brand", "commercial_intent": "buy", "condition_or_need": null, "english_equivalent": "brahmi tablets kerala ayurveda", "landing_page_type": "product_detail", "match_intent_core": "brahmi_tablet", "negative_keyword_needs": ["pearls", "capsule", "free", "home remedy"], "original_language": "normalized", "phrase_match_expansion_risk": "low", "product_family": "brahmi", "product_format": "tablet", "product_variant": null, "query_shape": "brand_product", "risk_flags": {"ambiguous_product_mapping": true, "competitor_term_present": false, "disease_term_present": false, "medical_claim_sensitive": false}}</t>
+        </is>
+      </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Negative Match</t>
+          <t>Phrase Match</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Navigational</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>MOF</t>
+          <t>BOF</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>negative_keywords</t>
+          <t>competitor_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
+          <t>Competitor + product query kept positive; routed to competitor_search_brahmi_pearls_x (Navigational, BOF).</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>brahmi tablet kerala ayurveda</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>brahmi tablet</t>
+          <t>stress aid tablets uses</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -2836,12 +3184,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>MOF</t>
+          <t>TOF</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2851,7 +3199,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
+          <t>Informational intent from LLM/rule</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -2860,7 +3208,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>brahmi tablet kerala ayurveda</t>
+          <t>stress free tablets uses</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -2876,12 +3224,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Navigational</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>MOF</t>
+          <t>TOF</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2891,7 +3239,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
+          <t>Informational intent from LLM/rule</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -3101,7 +3449,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "stress relief supplements", "landing_page_type": "product_detail", "match_intent_core": "stress_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "causes", "jobs", "yoga", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_relief_medicine", "product_format": "unknown", "product_variant": null, "query_shape": "product_only", "risk_flags": {"ambiguous_product_mapping": true, "competitor_term_present": false, "disease_term_present": false, "medical_claim_sensitive": true}}</t>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "condition", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "stress relief tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_relief", "negative_keyword_needs": ["free", "home remedy", "remedies", "symptoms", "causes", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "high", "product_family": "stress_relief_supplement", "product_format": "other", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": true, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -3153,22 +3501,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>fp_0002</t>
+          <t>fp_0001</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "stress relief supplements", "landing_page_type": "product_detail", "match_intent_core": "stress_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "causes", "jobs", "yoga", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_relief_medicine", "product_format": "tablet", "product_variant": null, "query_shape": "product_only", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": false, "medical_claim_sensitive": true}}</t>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "condition", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "stress relief tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_relief", "negative_keyword_needs": ["free", "home remedy", "remedies", "symptoms", "causes", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "high", "product_family": "stress_relief_supplement", "product_format": "other", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": true, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Phrase Match</t>
+          <t>Negative Match</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -3183,12 +3531,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>condition_search_brahmi_pearls_x</t>
+          <t>negative_keywords</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF).</t>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF). | Duplicate fingerprint group; kept 'stress relief medicine' as primary and marked this as negative.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -3205,17 +3553,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>stress relief pills</t>
+          <t>tension relief medicine</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>fp_0002</t>
+          <t>fp_0001</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "stress relief supplements", "landing_page_type": "product_detail", "match_intent_core": "stress_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "causes", "jobs", "yoga", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_relief_medicine", "product_format": "tablet", "product_variant": null, "query_shape": "product_only", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": false, "medical_claim_sensitive": true}}</t>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "condition", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "stress relief tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_relief", "negative_keyword_needs": ["free", "home remedy", "remedies", "symptoms", "causes", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "high", "product_family": "stress_relief_supplement", "product_format": "other", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": true, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -3245,12 +3593,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF). | Duplicate fingerprint group; kept 'stress reliever pills' as primary and marked this as negative.</t>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF). | Duplicate fingerprint group; kept 'stress relief medicine' as primary and marked this as negative.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>stress relief pills</t>
+          <t>tension relief medicine</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -3262,17 +3610,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>stress reliever supplement</t>
+          <t>stress relief tablet</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>fp_0003</t>
+          <t>fp_0002</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "stress relief supplements", "landing_page_type": "product_detail", "match_intent_core": "stress_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "causes", "jobs", "yoga", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_relief_supplement", "product_format": "other", "product_variant": null, "query_shape": "product_only", "risk_flags": {"ambiguous_product_mapping": true, "competitor_term_present": false, "disease_term_present": false, "medical_claim_sensitive": true}}</t>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "condition", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "stress relief tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_relief", "negative_keyword_needs": ["free", "home remedy", "remedies", "symptoms", "causes", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "high", "product_family": "stress_relief_supplement", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -3307,7 +3655,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>stress reliever supplement</t>
+          <t>stress relief tablet</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -3319,27 +3667,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>best stress relief medicine</t>
+          <t>stress relief pills</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>fp_0004</t>
+          <t>fp_0001</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "best", "condition_or_need": "stress", "english_equivalent": "stress relief supplements", "landing_page_type": "product_detail", "match_intent_core": "stress_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "causes", "cheap", "jobs", "yoga"], "original_language": "normalized", "phrase_match_expansion_risk": "high", "product_family": "stress_relief_medicine", "product_format": "unknown", "product_variant": null, "query_shape": "product_only", "risk_flags": {"ambiguous_product_mapping": true, "competitor_term_present": false, "disease_term_present": false, "medical_claim_sensitive": true}}</t>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "condition", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "stress relief tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_relief", "negative_keyword_needs": ["free", "home remedy", "remedies", "symptoms", "causes", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "high", "product_family": "stress_relief_supplement", "product_format": "other", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": true, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Phrase Match</t>
+          <t>Negative Match</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -3354,17 +3702,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>evaluation_search_brahmi_pearls_x</t>
+          <t>negative_keywords</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Evaluation/comparison style query; routed to evaluation_search_brahmi_pearls_x (Commercial, MOF).</t>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF). | Duplicate fingerprint group; kept 'stress relief medicine' as primary and marked this as negative.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>best stress relief medicine</t>
+          <t>stress relief pills</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -3376,27 +3724,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>anxiety and stress relief pills</t>
+          <t>stress tablets</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>fp_0005</t>
+          <t>fp_0002</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress_and_anxiety", "english_equivalent": "stress and anxiety relief supplements", "landing_page_type": "product_detail", "match_intent_core": "anxiety_and_stress_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "causes", "therapy", "yoga", "jobs", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_relief_medicine", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "condition", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "stress relief tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_relief", "negative_keyword_needs": ["free", "home remedy", "remedies", "symptoms", "causes", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "high", "product_family": "stress_relief_supplement", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Phrase Match</t>
+          <t>Negative Match</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -3411,17 +3759,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>condition_search_brahmi_pearls_x</t>
+          <t>negative_keywords</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF).</t>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF). | Duplicate fingerprint group; kept 'stress relief tablet' as primary and marked this as negative.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>anxiety and stress relief pills</t>
+          <t>stress tablets</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3433,27 +3781,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>stress and anxiety relief pills</t>
+          <t>anxiety and stress tablets</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>fp_0005</t>
+          <t>fp_0003</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress_and_anxiety", "english_equivalent": "stress and anxiety relief supplements", "landing_page_type": "product_detail", "match_intent_core": "anxiety_and_stress_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "causes", "therapy", "yoga", "jobs", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_relief_medicine", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "condition", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "anxiety_and_stress", "english_equivalent": "anxiety and stress relief tablets", "landing_page_type": "product_detail", "match_intent_core": "anxiety_and_stress_relief", "negative_keyword_needs": ["free", "home remedy", "remedies", "symptoms", "causes", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "high", "product_family": "stress_relief_supplement", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Negative Match</t>
+          <t>Phrase Match</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3468,17 +3816,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>negative_keywords</t>
+          <t>condition_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF). | Duplicate fingerprint group; kept 'anxiety and stress relief pills' as primary and marked this as negative.</t>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF).</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>stress and anxiety relief pills</t>
+          <t>anxiety and stress tablets</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3490,17 +3838,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>anxiety stress relief pills</t>
+          <t>stress free tablets</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>fp_0005</t>
+          <t>fp_0002</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress_and_anxiety", "english_equivalent": "stress and anxiety relief supplements", "landing_page_type": "product_detail", "match_intent_core": "anxiety_and_stress_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "causes", "therapy", "yoga", "jobs", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_relief_medicine", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "condition", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "stress relief tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_relief", "negative_keyword_needs": ["free", "home remedy", "remedies", "symptoms", "causes", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "high", "product_family": "stress_relief_supplement", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3530,12 +3878,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF). | Duplicate fingerprint group; kept 'anxiety and stress relief pills' as primary and marked this as negative.</t>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF). | Duplicate fingerprint group; kept 'stress relief tablet' as primary and marked this as negative.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>anxiety stress relief pills</t>
+          <t>stress free tablets</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3547,17 +3895,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>stress release pills</t>
+          <t>anxiety stress tablets</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>fp_0002</t>
+          <t>fp_0003</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "stress relief supplements", "landing_page_type": "product_detail", "match_intent_core": "stress_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "causes", "jobs", "yoga", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_relief_medicine", "product_format": "tablet", "product_variant": null, "query_shape": "product_only", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": false, "medical_claim_sensitive": true}}</t>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "condition", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "anxiety_and_stress", "english_equivalent": "anxiety and stress relief tablets", "landing_page_type": "product_detail", "match_intent_core": "anxiety_and_stress_relief", "negative_keyword_needs": ["free", "home remedy", "remedies", "symptoms", "causes", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "high", "product_family": "stress_relief_supplement", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3587,12 +3935,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF). | Duplicate fingerprint group; kept 'stress reliever pills' as primary and marked this as negative.</t>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF). | Duplicate fingerprint group; kept 'anxiety and stress tablets' as primary and marked this as negative.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>stress release pills</t>
+          <t>anxiety stress tablets</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -3604,17 +3952,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>stress control pills</t>
+          <t>stress reliever supplement</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>fp_0002</t>
+          <t>fp_0001</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "stress relief supplements", "landing_page_type": "product_detail", "match_intent_core": "stress_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "causes", "jobs", "yoga", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_relief_medicine", "product_format": "tablet", "product_variant": null, "query_shape": "product_only", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": false, "medical_claim_sensitive": true}}</t>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "condition", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "stress relief tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_relief", "negative_keyword_needs": ["free", "home remedy", "remedies", "symptoms", "causes", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "high", "product_family": "stress_relief_supplement", "product_format": "other", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": true, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3644,12 +3992,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF). | Duplicate fingerprint group; kept 'stress reliever pills' as primary and marked this as negative.</t>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF). | Duplicate fingerprint group; kept 'stress relief medicine' as primary and marked this as negative.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>stress control pills</t>
+          <t>stress reliever supplement</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -3661,17 +4009,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>stress and anxiety relief supplements</t>
+          <t>himalaya stress relief tablet</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>fp_0006</t>
+          <t>fp_0004</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{"ad_copy_angle": "education", "ad_group_intent": "condition", "audience": null, "brand_scope": "generic", "commercial_intent": "informational", "condition_or_need": "stress_anxiety", "english_equivalent": "stress and anxiety relief supplements", "landing_page_type": "category", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "jobs", "career"], "original_language": "normalized", "phrase_match_expansion_risk": "high", "product_family": "stress_anxiety_relief_supplement", "product_format": "unknown", "product_variant": null, "query_shape": "condition_solution", "risk_flags": {"ambiguous_product_mapping": true, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+          <t>{"ad_copy_angle": "comparison", "ad_group_intent": "competitor", "audience": null, "brand_scope": "competitor", "commercial_intent": "buy", "condition_or_need": "stress_and_anxiety", "english_equivalent": "himalaya stress relief tablet", "landing_page_type": "comparison_page", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "jobs", "how to", "symptoms", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "high", "product_family": "stress_anxiety_relief", "product_format": "tablet", "product_variant": null, "query_shape": "competitor_product", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": true, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3696,17 +4044,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>condition_search_brahmi_pearls_x</t>
+          <t>competitor_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF).</t>
+          <t>Classified as Commercial at MOF; routed to competitor_search_brahmi_pearls_x.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>stress and anxiety relief supplements</t>
+          <t>himalaya stress relief tablet</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -3718,27 +4066,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>anxiety stress relief supplement</t>
+          <t>best stress relief medicine</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>fp_0006</t>
+          <t>fp_0005</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{"ad_copy_angle": "education", "ad_group_intent": "condition", "audience": null, "brand_scope": "generic", "commercial_intent": "informational", "condition_or_need": "stress_anxiety", "english_equivalent": "stress and anxiety relief supplements", "landing_page_type": "category", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "jobs", "career"], "original_language": "normalized", "phrase_match_expansion_risk": "high", "product_family": "stress_anxiety_relief_supplement", "product_format": "unknown", "product_variant": null, "query_shape": "condition_solution", "risk_flags": {"ambiguous_product_mapping": true, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+          <t>{"ad_copy_angle": "review_social_proof", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "best", "condition_or_need": "stress_and_anxiety", "english_equivalent": "best stress relief tablets", "landing_page_type": "comparison_page", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "side effects", "jobs", "how to"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_anxiety_relief", "product_format": "unknown", "product_variant": null, "query_shape": "commercial_modifier", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Negative Match</t>
+          <t>Phrase Match</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -3753,17 +4101,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>negative_keywords</t>
+          <t>evaluation_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF). | Duplicate fingerprint group; kept 'stress and anxiety relief supplements' as primary and marked this as negative.</t>
+          <t>Evaluation/comparison style query; routed to evaluation_search_brahmi_pearls_x (Commercial, MOF).</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>anxiety stress relief supplement</t>
+          <t>best stress relief medicine</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -3775,7 +4123,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>stress anxiety relief supplements</t>
+          <t>tension relief tablets</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3785,17 +4133,17 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{"ad_copy_angle": "education", "ad_group_intent": "condition", "audience": null, "brand_scope": "generic", "commercial_intent": "informational", "condition_or_need": "stress_anxiety", "english_equivalent": "stress and anxiety relief supplements", "landing_page_type": "category", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "jobs", "career"], "original_language": "normalized", "phrase_match_expansion_risk": "high", "product_family": "stress_anxiety_relief_supplement", "product_format": "unknown", "product_variant": null, "query_shape": "condition_solution", "risk_flags": {"ambiguous_product_mapping": true, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress_and_anxiety", "english_equivalent": "tension relief tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "side effects", "jobs", "himalaya", "patanjali", "patent", "how to"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_anxiety_relief", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Negative Match</t>
+          <t>Phrase Match</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3810,17 +4158,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>negative_keywords</t>
+          <t>condition_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF). | Duplicate fingerprint group; kept 'stress and anxiety relief supplements' as primary and marked this as negative.</t>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF).</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>stress anxiety relief supplements</t>
+          <t>tension relief tablets</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -3832,7 +4180,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>stress away pills</t>
+          <t>stress reducing tablets</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3842,7 +4190,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{"ad_copy_angle": "education", "ad_group_intent": "condition", "audience": null, "brand_scope": "generic", "commercial_intent": "informational", "condition_or_need": "stress_anxiety", "english_equivalent": "stress and anxiety relief supplements", "landing_page_type": "category", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "jobs", "career"], "original_language": "normalized", "phrase_match_expansion_risk": "high", "product_family": "stress_anxiety_relief_supplement", "product_format": "unknown", "product_variant": null, "query_shape": "condition_solution", "risk_flags": {"ambiguous_product_mapping": true, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress_and_anxiety", "english_equivalent": "tension relief tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "side effects", "jobs", "himalaya", "patanjali", "patent", "how to"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_anxiety_relief", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3872,12 +4220,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF). | Duplicate fingerprint group; kept 'stress and anxiety relief supplements' as primary and marked this as negative.</t>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF). | Duplicate fingerprint group; kept 'tension relief tablets' as primary and marked this as negative.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>stress away pills</t>
+          <t>stress reducing tablets</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -3889,7 +4237,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>sleeping pills for stress relief</t>
+          <t>anxiety and stress relief pills</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3899,7 +4247,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{"ad_copy_angle": "education", "ad_group_intent": "condition", "audience": null, "brand_scope": "generic", "commercial_intent": "informational", "condition_or_need": "stress_anxiety", "english_equivalent": "stress and anxiety relief supplements", "landing_page_type": "category", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "jobs", "career"], "original_language": "normalized", "phrase_match_expansion_risk": "high", "product_family": "stress_anxiety_relief_supplement", "product_format": "unknown", "product_variant": null, "query_shape": "condition_solution", "risk_flags": {"ambiguous_product_mapping": true, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress_and_anxiety", "english_equivalent": "tension relief tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "side effects", "jobs", "himalaya", "patanjali", "patent", "how to"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_anxiety_relief", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3929,12 +4277,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF). | Duplicate fingerprint group; kept 'stress and anxiety relief supplements' as primary and marked this as negative.</t>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF). | Duplicate fingerprint group; kept 'tension relief tablets' as primary and marked this as negative.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>sleeping pills for stress relief</t>
+          <t>anxiety and stress relief pills</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -3946,27 +4294,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ayurvedic stress relief medicine</t>
+          <t>anxiety and stress relief tablets</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>fp_0007</t>
+          <t>fp_0006</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "condition", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress_anxiety", "english_equivalent": "ayurvedic stress relief medicine", "landing_page_type": "category", "match_intent_core": "ayurvedic_stress_relief_medicine", "negative_keyword_needs": ["free", "home remedy"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "ayurvedic_medicine", "product_format": "other", "product_variant": null, "query_shape": "condition_solution", "risk_flags": {"ambiguous_product_mapping": true, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress_and_anxiety", "english_equivalent": "tension relief tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "side effects", "jobs", "himalaya", "patanjali", "patent", "how to"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_anxiety_relief", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Phrase Match</t>
+          <t>Negative Match</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3981,17 +4329,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>condition_search_brahmi_pearls_x</t>
+          <t>negative_keywords</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF).</t>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF). | Duplicate fingerprint group; kept 'tension relief tablets' as primary and marked this as negative.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>ayurvedic stress relief medicine</t>
+          <t>anxiety and stress relief tablets</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -4003,17 +4351,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>stress relief medicine in ayurveda</t>
+          <t>stress and anxiety relief pills</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>fp_0007</t>
+          <t>fp_0006</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "condition", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress_anxiety", "english_equivalent": "ayurvedic stress relief medicine", "landing_page_type": "category", "match_intent_core": "ayurvedic_stress_relief_medicine", "negative_keyword_needs": ["free", "home remedy"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "ayurvedic_medicine", "product_format": "other", "product_variant": null, "query_shape": "condition_solution", "risk_flags": {"ambiguous_product_mapping": true, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress_and_anxiety", "english_equivalent": "tension relief tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "side effects", "jobs", "himalaya", "patanjali", "patent", "how to"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_anxiety_relief", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -4043,12 +4391,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF). | Duplicate fingerprint group; kept 'ayurvedic stress relief medicine' as primary and marked this as negative.</t>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF). | Duplicate fingerprint group; kept 'tension relief tablets' as primary and marked this as negative.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>stress relief medicine in ayurveda</t>
+          <t>stress and anxiety relief pills</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -4060,52 +4408,52 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>brahmi pearls</t>
+          <t>anxiety stress relief pills</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>fp_0008</t>
+          <t>fp_0006</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{"ad_copy_angle": "buy_now", "ad_group_intent": "brand_product", "audience": null, "brand_scope": "brand", "commercial_intent": "buy", "condition_or_need": null, "english_equivalent": "brahmi pearls kerala ayurveda", "landing_page_type": "product_detail", "match_intent_core": "brahmi_pearls", "negative_keyword_needs": ["free", "home remedy", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "low", "product_family": "brahmi_pearls", "product_format": "capsule", "product_variant": null, "query_shape": "brand_product", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": false, "medical_claim_sensitive": false}}</t>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress_and_anxiety", "english_equivalent": "tension relief tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "side effects", "jobs", "himalaya", "patanjali", "patent", "how to"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_anxiety_relief", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Phrase Match</t>
+          <t>Negative Match</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Navigational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>BOF</t>
+          <t>MOF</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>competitor_search_brahmi_pearls_x</t>
+          <t>negative_keywords</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Competitor + product query kept positive; routed to competitor_search_brahmi_pearls_x (Navigational, BOF).</t>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF). | Duplicate fingerprint group; kept 'tension relief tablets' as primary and marked this as negative.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>brahmi pearls</t>
+          <t>anxiety stress relief pills</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -4117,17 +4465,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>kerala ayurveda brahmi pearls</t>
+          <t>stress release tablets</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>fp_0008</t>
+          <t>fp_0006</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{"ad_copy_angle": "buy_now", "ad_group_intent": "brand_product", "audience": null, "brand_scope": "brand", "commercial_intent": "buy", "condition_or_need": null, "english_equivalent": "brahmi pearls kerala ayurveda", "landing_page_type": "product_detail", "match_intent_core": "brahmi_pearls", "negative_keyword_needs": ["free", "home remedy", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "low", "product_family": "brahmi_pearls", "product_format": "capsule", "product_variant": null, "query_shape": "brand_product", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": false, "medical_claim_sensitive": false}}</t>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress_and_anxiety", "english_equivalent": "tension relief tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "side effects", "jobs", "himalaya", "patanjali", "patent", "how to"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_anxiety_relief", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4142,12 +4490,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Navigational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>BOF</t>
+          <t>MOF</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -4157,12 +4505,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Competitor + product query kept positive; routed to competitor_search_brahmi_pearls_x (Navigational, BOF). | Duplicate fingerprint group; kept 'brahmi pearls' as primary and marked this as negative.</t>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF). | Duplicate fingerprint group; kept 'tension relief tablets' as primary and marked this as negative.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>kerala ayurveda brahmi pearls</t>
+          <t>stress release tablets</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -4174,17 +4522,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>brahmi pearls kerala ayurveda</t>
+          <t>stress release pills</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>fp_0008</t>
+          <t>fp_0006</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{"ad_copy_angle": "buy_now", "ad_group_intent": "brand_product", "audience": null, "brand_scope": "brand", "commercial_intent": "buy", "condition_or_need": null, "english_equivalent": "brahmi pearls kerala ayurveda", "landing_page_type": "product_detail", "match_intent_core": "brahmi_pearls", "negative_keyword_needs": ["free", "home remedy", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "low", "product_family": "brahmi_pearls", "product_format": "capsule", "product_variant": null, "query_shape": "brand_product", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": false, "medical_claim_sensitive": false}}</t>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress_and_anxiety", "english_equivalent": "tension relief tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "side effects", "jobs", "himalaya", "patanjali", "patent", "how to"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_anxiety_relief", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4199,12 +4547,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Navigational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>BOF</t>
+          <t>MOF</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -4214,12 +4562,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Competitor + product query kept positive; routed to competitor_search_brahmi_pearls_x (Navigational, BOF). | Duplicate fingerprint group; kept 'brahmi pearls' as primary and marked this as negative.</t>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF). | Duplicate fingerprint group; kept 'tension relief tablets' as primary and marked this as negative.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>brahmi pearls kerala ayurveda</t>
+          <t>stress release pills</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -4231,19 +4579,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>tension relief medicine</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
+          <t>stress control pills</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>fp_0007</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress_and_anxiety", "english_equivalent": "stress control tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "jobs"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_relief_supplement", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Negative Match</t>
+          <t>Phrase Match</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4258,25 +4614,41 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>negative_keywords</t>
+          <t>condition_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Ambiguous/off-primary-use-case intent</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF).</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stress control pills</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>stress relief tablet</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
+          <t>stress relieving tablets</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>fp_0007</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress_and_anxiety", "english_equivalent": "stress control tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "jobs"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_relief_supplement", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>Negative</t>
@@ -4304,20 +4676,36 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF). | Duplicate fingerprint group; kept 'stress control pills' as primary and marked this as negative.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>stress relieving tablets</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>stress tablets</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
+          <t>mental stress relief tablets</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>fp_0007</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress_and_anxiety", "english_equivalent": "stress control tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "jobs"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_relief_supplement", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>Negative</t>
@@ -4345,20 +4733,36 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF). | Duplicate fingerprint group; kept 'stress control pills' as primary and marked this as negative.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>mental stress relief tablets</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>anxiety and stress tablets</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
+          <t>stress control tablets</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>fp_0007</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress_and_anxiety", "english_equivalent": "stress control tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "jobs"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_relief_supplement", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
           <t>Negative</t>
@@ -4386,28 +4790,44 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF). | Duplicate fingerprint group; kept 'stress control pills' as primary and marked this as negative.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stress control tablets</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>stress free tablets</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
+          <t>stress and anxiety relief supplements</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>fp_0008</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress_and_anxiety", "english_equivalent": "stress and anxiety relief supplements", "landing_page_type": "product_detail", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "jobs"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_relief_supplement", "product_format": "other", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Negative Match</t>
+          <t>Phrase Match</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -4422,25 +4842,41 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>negative_keywords</t>
+          <t>condition_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF).</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>stress and anxiety relief supplements</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>anxiety stress tablets</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
+          <t>anxiety stress relief supplement</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>fp_0008</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress_and_anxiety", "english_equivalent": "stress and anxiety relief supplements", "landing_page_type": "product_detail", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "jobs"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_relief_supplement", "product_format": "other", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>Negative</t>
@@ -4468,20 +4904,36 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF). | Duplicate fingerprint group; kept 'stress and anxiety relief supplements' as primary and marked this as negative.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>anxiety stress relief supplement</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>himalaya stress relief tablet</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
+          <t>stress anxiety relief supplements</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>fp_0008</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress_and_anxiety", "english_equivalent": "stress and anxiety relief supplements", "landing_page_type": "product_detail", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "jobs"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_relief_supplement", "product_format": "other", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
           <t>Negative</t>
@@ -4509,20 +4961,36 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF). | Duplicate fingerprint group; kept 'stress and anxiety relief supplements' as primary and marked this as negative.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>stress anxiety relief supplements</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>tension relief tablets</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
+          <t>stress away pills</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>fp_0007</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress_and_anxiety", "english_equivalent": "stress control tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "jobs"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_relief_supplement", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
           <t>Negative</t>
@@ -4550,28 +5018,44 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF). | Duplicate fingerprint group; kept 'stress control pills' as primary and marked this as negative.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>stress away pills</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>stress reducing tablets</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
+          <t>himalaya stress tablets</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>fp_0009</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "comparison", "ad_group_intent": "competitor", "audience": null, "brand_scope": "competitor", "commercial_intent": "buy", "condition_or_need": "stress_and_anxiety", "english_equivalent": "himalaya stress tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "jobs"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_relief_supplement", "product_format": "tablet", "product_variant": null, "query_shape": "brand_product", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": true, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Negative Match</t>
+          <t>Phrase Match</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -4586,25 +5070,41 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>negative_keywords</t>
+          <t>competitor_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+          <t>Classified as Commercial at MOF; routed to competitor_search_brahmi_pearls_x.</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>himalaya stress tablets</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>anxiety and stress relief tablets</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
+          <t>mind stress relief tablets</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>fp_0007</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress_and_anxiety", "english_equivalent": "stress control tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "jobs"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_relief_supplement", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
           <t>Negative</t>
@@ -4632,28 +5132,44 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF). | Duplicate fingerprint group; kept 'stress control pills' as primary and marked this as negative.</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>mind stress relief tablets</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>stress release tablets</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
+          <t>mental stress tablets</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>fp_0010</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "mental stress relief tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_relief_tablet", "negative_keyword_needs": ["free", "home remedy", "home remedies", "prescription"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "ayurvedic_stress_relief_medicine", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Negative Match</t>
+          <t>Phrase Match</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -4668,25 +5184,41 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>negative_keywords</t>
+          <t>condition_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF).</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>mental stress tablets</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>stress relieving tablets</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
+          <t>stress management tablets</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>fp_0010</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "mental stress relief tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_relief_tablet", "negative_keyword_needs": ["free", "home remedy", "home remedies", "prescription"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "ayurvedic_stress_relief_medicine", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
           <t>Negative</t>
@@ -4714,20 +5246,36 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF). | Duplicate fingerprint group; kept 'mental stress tablets' as primary and marked this as negative.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>stress management tablets</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>mental stress relief tablets</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
+          <t>stress relief ayurvedic tablets</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>fp_0010</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "mental stress relief tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_relief_tablet", "negative_keyword_needs": ["free", "home remedy", "home remedies", "prescription"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "ayurvedic_stress_relief_medicine", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
           <t>Negative</t>
@@ -4755,20 +5303,36 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF). | Duplicate fingerprint group; kept 'mental stress tablets' as primary and marked this as negative.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stress relief ayurvedic tablets</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>stress control tablets</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
+          <t>stress relief tablets in ayurveda</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>fp_0010</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "mental stress relief tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_relief_tablet", "negative_keyword_needs": ["free", "home remedy", "home remedies", "prescription"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "ayurvedic_stress_relief_medicine", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
           <t>Negative</t>
@@ -4796,28 +5360,44 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF). | Duplicate fingerprint group; kept 'mental stress tablets' as primary and marked this as negative.</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>stress relief tablets in ayurveda</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>himalaya stress tablets</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
+          <t>best stress relief tablets</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>fp_0011</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "comparison", "ad_group_intent": "evaluation", "audience": null, "brand_scope": "generic", "commercial_intent": "best", "condition_or_need": "stress", "english_equivalent": "best stress relief tablets", "landing_page_type": "comparison_page", "match_intent_core": "stress_relief_tablet", "negative_keyword_needs": ["free", "home remedy", "home remedies", "prescription"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "ayurvedic_stress_relief_medicine", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Negative Match</t>
+          <t>Phrase Match</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4832,33 +5412,49 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>negative_keywords</t>
+          <t>evaluation_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+          <t>Evaluation/comparison style query; routed to evaluation_search_brahmi_pearls_x (Commercial, MOF).</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>best stress relief tablets</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>mind stress relief tablets</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
+          <t>sleeping pills for stress relief</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>fp_0012</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "education", "ad_group_intent": "informational", "audience": null, "brand_scope": "generic", "commercial_intent": "informational", "condition_or_need": "stress", "english_equivalent": "sleeping pills for stress relief", "landing_page_type": "educational_page", "match_intent_core": "sleeping_pills_for_stress_relief", "negative_keyword_needs": ["prescription", "psychiatrist", "psychologist", "free"], "original_language": "normalized", "phrase_match_expansion_risk": "high", "product_family": "sleep_aids", "product_format": "tablet", "product_variant": null, "query_shape": "condition_solution", "risk_flags": {"ambiguous_product_mapping": true, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Negative Match</t>
+          <t>Phrase Match</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4873,25 +5469,41 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>negative_keywords</t>
+          <t>condition_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF).</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>sleeping pills for stress relief</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>stress aid tablets uses</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
+          <t>stress buster tablet</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>fp_0010</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "mental stress relief tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_relief_tablet", "negative_keyword_needs": ["free", "home remedy", "home remedies", "prescription"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "ayurvedic_stress_relief_medicine", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
           <t>Negative</t>
@@ -4904,12 +5516,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>TOF</t>
+          <t>MOF</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4919,20 +5531,36 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+          <t>Direct product-intent query; routed to product_search_brahmi_pearls_x (Commercial, MOF). | Duplicate fingerprint group; kept 'mental stress tablets' as primary and marked this as negative.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>stress buster tablet</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>mental stress tablets</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
+          <t>stress reliever tablet</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>fp_0010</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "mental stress relief tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_relief_tablet", "negative_keyword_needs": ["free", "home remedy", "home remedies", "prescription"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "ayurvedic_stress_relief_medicine", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
           <t>Negative</t>
@@ -4960,20 +5588,36 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
+          <t>Direct product-intent query; routed to product_search_brahmi_pearls_x (Commercial, MOF). | Duplicate fingerprint group; kept 'mental stress tablets' as primary and marked this as negative.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>stress reliever tablet</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>stress management tablets</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
+          <t>tablet for tension relief</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>fp_0010</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "mental stress relief tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_relief_tablet", "negative_keyword_needs": ["free", "home remedy", "home remedies", "prescription"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "ayurvedic_stress_relief_medicine", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
           <t>Negative</t>
@@ -5001,28 +5645,44 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF). | Duplicate fingerprint group; kept 'mental stress tablets' as primary and marked this as negative.</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>tablet for tension relief</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>stress relief ayurvedic tablets</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
+          <t>ayurvedic stress relief medicine</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>fp_0013</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "ayurvedic stress relief medicine", "landing_page_type": "product_detail", "match_intent_core": "ayurvedic_stress_relief_medicine", "negative_keyword_needs": ["free", "home remedy", "home remedies", "prescription"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "ayurvedic_stress_relief_medicine", "product_format": "unknown", "product_variant": null, "query_shape": "product_only", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Negative Match</t>
+          <t>Phrase Match</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -5037,33 +5697,49 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>negative_keywords</t>
+          <t>condition_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF).</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>ayurvedic stress relief medicine</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>stress relief tablets in ayurveda</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
+          <t>stress free tablets ayurvedic</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>fp_0014</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "condition", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "ayurvedic stress relief tablets", "landing_page_type": "condition_page", "match_intent_core": "stress_relief", "negative_keyword_needs": ["home remedy", "free", "symptoms", "causes"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "ayurvedic_stress_medicine", "product_format": "tablet", "product_variant": null, "query_shape": "condition_solution", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Negative Match</t>
+          <t>Phrase Match</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -5078,25 +5754,41 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>negative_keywords</t>
+          <t>condition_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF).</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>stress free tablets ayurvedic</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>best stress relief tablets</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
+          <t>stress relief medicine in ayurveda</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>fp_0014</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "condition", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "ayurvedic stress relief tablets", "landing_page_type": "condition_page", "match_intent_core": "stress_relief", "negative_keyword_needs": ["home remedy", "free", "symptoms", "causes"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "ayurvedic_stress_medicine", "product_format": "tablet", "product_variant": null, "query_shape": "condition_solution", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
           <t>Negative</t>
@@ -5124,20 +5816,36 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF). | Duplicate fingerprint group; kept 'stress free tablets ayurvedic' as primary and marked this as negative.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>stress relief medicine in ayurveda</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>stress buster tablet</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
+          <t>ayurvedic stress tablets</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>fp_0014</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "condition", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "ayurvedic stress relief tablets", "landing_page_type": "condition_page", "match_intent_core": "stress_relief", "negative_keyword_needs": ["home remedy", "free", "symptoms", "causes"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "ayurvedic_stress_medicine", "product_format": "tablet", "product_variant": null, "query_shape": "condition_solution", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
           <t>Negative</t>
@@ -5165,20 +5873,36 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF). | Duplicate fingerprint group; kept 'stress free tablets ayurvedic' as primary and marked this as negative.</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>ayurvedic stress tablets</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>stress free tablets uses</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
+          <t>stress tablets ayurvedic</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>fp_0014</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "condition", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "ayurvedic stress relief tablets", "landing_page_type": "condition_page", "match_intent_core": "stress_relief", "negative_keyword_needs": ["home remedy", "free", "symptoms", "causes"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "ayurvedic_stress_medicine", "product_format": "tablet", "product_variant": null, "query_shape": "condition_solution", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
           <t>Negative</t>
@@ -5191,12 +5915,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Informational</t>
+          <t>Commercial</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>TOF</t>
+          <t>MOF</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5206,28 +5930,44 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+          <t>Condition-solution intent aligned to product use case; routed to condition_search_brahmi_pearls_x (Commercial, MOF). | Duplicate fingerprint group; kept 'stress free tablets ayurvedic' as primary and marked this as negative.</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>stress tablets ayurvedic</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>stress reliever tablet</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
+          <t>brahmi pearls</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>fp_0015</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": null, "english_equivalent": "brahmi pearls", "landing_page_type": "product_detail", "match_intent_core": "brahmi_pearls", "negative_keyword_needs": ["tablet", "free", "home remedy"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "brahmi", "product_format": "capsule", "product_variant": null, "query_shape": "product_only", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": false, "medical_claim_sensitive": false}}</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Negative Match</t>
+          <t>Phrase Match</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -5242,33 +5982,49 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>negative_keywords</t>
+          <t>competitor_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
+          <t>Competitor + product query kept positive; routed to competitor_search_brahmi_pearls_x (Commercial, MOF).</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>brahmi pearls</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>tablet for tension relief</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr"/>
+          <t>brahmi tablet</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>fp_0016</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": null, "english_equivalent": "brahmi tablets", "landing_page_type": "product_detail", "match_intent_core": "brahmi_tablet", "negative_keyword_needs": ["pearls", "capsule", "free", "home remedy"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "brahmi", "product_format": "tablet", "product_variant": null, "query_shape": "product_only", "risk_flags": {"ambiguous_product_mapping": true, "competitor_term_present": false, "disease_term_present": false, "medical_claim_sensitive": false}}</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Negative Match</t>
+          <t>Phrase Match</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5283,66 +6039,98 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>negative_keywords</t>
+          <t>competitor_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
+          <t>Competitor + product query kept positive; routed to competitor_search_brahmi_pearls_x (Commercial, MOF).</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>brahmi tablet</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>stress free tablets ayurvedic</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr"/>
+          <t>kerala ayurveda brahmi pearls</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>fp_0017</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "brand_trust", "ad_group_intent": "brand_product", "audience": null, "brand_scope": "brand", "commercial_intent": "buy", "condition_or_need": null, "english_equivalent": "brahmi pearls kerala ayurveda", "landing_page_type": "product_detail", "match_intent_core": "brahmi_pearls", "negative_keyword_needs": ["tablet", "home remedy", "free"], "original_language": "normalized", "phrase_match_expansion_risk": "low", "product_family": "brahmi", "product_format": "capsule", "product_variant": null, "query_shape": "brand_product", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": false, "medical_claim_sensitive": false}}</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Negative Match</t>
+          <t>Phrase Match</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Navigational</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>MOF</t>
+          <t>BOF</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>negative_keywords</t>
+          <t>competitor_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
+          <t>Competitor + product query kept positive; routed to competitor_search_brahmi_pearls_x (Navigational, BOF).</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>kerala ayurveda brahmi pearls</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ayurvedic stress tablets</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
+          <t>brahmi pearls kerala ayurveda</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>fp_0017</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "brand_trust", "ad_group_intent": "brand_product", "audience": null, "brand_scope": "brand", "commercial_intent": "buy", "condition_or_need": null, "english_equivalent": "brahmi pearls kerala ayurveda", "landing_page_type": "product_detail", "match_intent_core": "brahmi_pearls", "negative_keyword_needs": ["tablet", "home remedy", "free"], "original_language": "normalized", "phrase_match_expansion_risk": "low", "product_family": "brahmi", "product_format": "capsule", "product_variant": null, "query_shape": "brand_product", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": false, "medical_claim_sensitive": false}}</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr">
         <is>
           <t>Negative</t>
@@ -5355,12 +6143,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Navigational</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>MOF</t>
+          <t>BOF</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -5370,57 +6158,81 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
+          <t>Competitor + product query kept positive; routed to competitor_search_brahmi_pearls_x (Navigational, BOF). | Duplicate fingerprint group; kept 'kerala ayurveda brahmi pearls' as primary and marked this as negative.</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>brahmi pearls kerala ayurveda</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>stress tablets ayurvedic</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
+          <t>brahmi tablet kerala ayurveda</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>fp_0018</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "brand_trust", "ad_group_intent": "brand_product", "audience": null, "brand_scope": "brand", "commercial_intent": "buy", "condition_or_need": null, "english_equivalent": "brahmi tablets kerala ayurveda", "landing_page_type": "product_detail", "match_intent_core": "brahmi_tablet", "negative_keyword_needs": ["pearls", "capsule", "free", "home remedy"], "original_language": "normalized", "phrase_match_expansion_risk": "low", "product_family": "brahmi", "product_format": "tablet", "product_variant": null, "query_shape": "brand_product", "risk_flags": {"ambiguous_product_mapping": true, "competitor_term_present": false, "disease_term_present": false, "medical_claim_sensitive": false}}</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Negative Match</t>
+          <t>Phrase Match</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Navigational</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>MOF</t>
+          <t>BOF</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>negative_keywords</t>
+          <t>competitor_search_brahmi_pearls_x</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
+          <t>Competitor + product query kept positive; routed to competitor_search_brahmi_pearls_x (Navigational, BOF).</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>brahmi tablet kerala ayurveda</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>english</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>brahmi tablet</t>
+          <t>stress aid tablets uses</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
@@ -5437,12 +6249,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>MOF</t>
+          <t>TOF</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -5452,7 +6264,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
+          <t>Informational intent from LLM/rule</t>
         </is>
       </c>
       <c r="J51" t="inlineStr"/>
@@ -5461,7 +6273,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>brahmi tablet kerala ayurveda</t>
+          <t>stress free tablets uses</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
@@ -5478,12 +6290,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Navigational</t>
+          <t>Informational</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>MOF</t>
+          <t>TOF</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -5493,7 +6305,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Wrong product format</t>
+          <t>Informational intent from LLM/rule</t>
         </is>
       </c>
       <c r="J52" t="inlineStr"/>
@@ -5633,7 +6445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5666,15 +6478,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "stress relief supplements", "landing_page_type": "product_detail", "match_intent_core": "stress_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "causes", "jobs", "yoga", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_relief_medicine", "product_format": "unknown", "product_variant": null, "query_shape": "product_only", "risk_flags": {"ambiguous_product_mapping": true, "competitor_term_present": false, "disease_term_present": false, "medical_claim_sensitive": true}}</t>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "condition", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "stress relief tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_relief", "negative_keyword_needs": ["free", "home remedy", "remedies", "symptoms", "causes", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "high", "product_family": "stress_relief_supplement", "product_format": "other", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": true, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>stress relief medicine</t>
+          <t>stress relief medicine, stress reliever pills, tension relief medicine, stress relief pills, stress reliever supplement</t>
         </is>
       </c>
     </row>
@@ -5686,15 +6498,15 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "stress relief supplements", "landing_page_type": "product_detail", "match_intent_core": "stress_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "causes", "jobs", "yoga", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_relief_medicine", "product_format": "tablet", "product_variant": null, "query_shape": "product_only", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": false, "medical_claim_sensitive": true}}</t>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "condition", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "stress relief tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_relief", "negative_keyword_needs": ["free", "home remedy", "remedies", "symptoms", "causes", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "high", "product_family": "stress_relief_supplement", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>stress reliever pills, stress relief pills, stress release pills, stress control pills</t>
+          <t>stress relief tablet, stress tablets, stress free tablets</t>
         </is>
       </c>
     </row>
@@ -5706,15 +6518,15 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "stress relief supplements", "landing_page_type": "product_detail", "match_intent_core": "stress_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "causes", "jobs", "yoga", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_relief_supplement", "product_format": "other", "product_variant": null, "query_shape": "product_only", "risk_flags": {"ambiguous_product_mapping": true, "competitor_term_present": false, "disease_term_present": false, "medical_claim_sensitive": true}}</t>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "condition", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "anxiety_and_stress", "english_equivalent": "anxiety and stress relief tablets", "landing_page_type": "product_detail", "match_intent_core": "anxiety_and_stress_relief", "negative_keyword_needs": ["free", "home remedy", "remedies", "symptoms", "causes", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "high", "product_family": "stress_relief_supplement", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>stress reliever supplement</t>
+          <t>anxiety and stress tablets, anxiety stress tablets</t>
         </is>
       </c>
     </row>
@@ -5726,7 +6538,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "best", "condition_or_need": "stress", "english_equivalent": "stress relief supplements", "landing_page_type": "product_detail", "match_intent_core": "stress_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "causes", "cheap", "jobs", "yoga"], "original_language": "normalized", "phrase_match_expansion_risk": "high", "product_family": "stress_relief_medicine", "product_format": "unknown", "product_variant": null, "query_shape": "product_only", "risk_flags": {"ambiguous_product_mapping": true, "competitor_term_present": false, "disease_term_present": false, "medical_claim_sensitive": true}}</t>
+          <t>{"ad_copy_angle": "comparison", "ad_group_intent": "competitor", "audience": null, "brand_scope": "competitor", "commercial_intent": "buy", "condition_or_need": "stress_and_anxiety", "english_equivalent": "himalaya stress relief tablet", "landing_page_type": "comparison_page", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "jobs", "how to", "symptoms", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "high", "product_family": "stress_anxiety_relief", "product_format": "tablet", "product_variant": null, "query_shape": "competitor_product", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": true, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -5734,7 +6546,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>best stress relief medicine</t>
+          <t>himalaya stress relief tablet</t>
         </is>
       </c>
     </row>
@@ -5746,15 +6558,15 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress_and_anxiety", "english_equivalent": "stress and anxiety relief supplements", "landing_page_type": "product_detail", "match_intent_core": "anxiety_and_stress_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "causes", "therapy", "yoga", "jobs", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_relief_medicine", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+          <t>{"ad_copy_angle": "review_social_proof", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "best", "condition_or_need": "stress_and_anxiety", "english_equivalent": "best stress relief tablets", "landing_page_type": "comparison_page", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "side effects", "jobs", "how to"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_anxiety_relief", "product_format": "unknown", "product_variant": null, "query_shape": "commercial_modifier", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>anxiety and stress relief pills, stress and anxiety relief pills, anxiety stress relief pills</t>
+          <t>best stress relief medicine</t>
         </is>
       </c>
     </row>
@@ -5766,15 +6578,15 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{"ad_copy_angle": "education", "ad_group_intent": "condition", "audience": null, "brand_scope": "generic", "commercial_intent": "informational", "condition_or_need": "stress_anxiety", "english_equivalent": "stress and anxiety relief supplements", "landing_page_type": "category", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "jobs", "career"], "original_language": "normalized", "phrase_match_expansion_risk": "high", "product_family": "stress_anxiety_relief_supplement", "product_format": "unknown", "product_variant": null, "query_shape": "condition_solution", "risk_flags": {"ambiguous_product_mapping": true, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress_and_anxiety", "english_equivalent": "tension relief tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "side effects", "jobs", "himalaya", "patanjali", "patent", "how to"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_anxiety_relief", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>stress and anxiety relief supplements, anxiety stress relief supplement, stress anxiety relief supplements, stress away pills, sleeping pills for stress relief</t>
+          <t>tension relief tablets, stress reducing tablets, anxiety and stress relief pills, anxiety and stress relief tablets, stress and anxiety relief pills, anxiety stress relief pills, stress release tablets, stress release pills</t>
         </is>
       </c>
     </row>
@@ -5786,15 +6598,15 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "condition", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress_anxiety", "english_equivalent": "ayurvedic stress relief medicine", "landing_page_type": "category", "match_intent_core": "ayurvedic_stress_relief_medicine", "negative_keyword_needs": ["free", "home remedy"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "ayurvedic_medicine", "product_format": "other", "product_variant": null, "query_shape": "condition_solution", "risk_flags": {"ambiguous_product_mapping": true, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress_and_anxiety", "english_equivalent": "stress control tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "jobs"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_relief_supplement", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ayurvedic stress relief medicine, stress relief medicine in ayurveda</t>
+          <t>stress control pills, stress relieving tablets, mental stress relief tablets, stress control tablets, stress away pills, mind stress relief tablets</t>
         </is>
       </c>
     </row>
@@ -5806,7 +6618,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{"ad_copy_angle": "buy_now", "ad_group_intent": "brand_product", "audience": null, "brand_scope": "brand", "commercial_intent": "buy", "condition_or_need": null, "english_equivalent": "brahmi pearls kerala ayurveda", "landing_page_type": "product_detail", "match_intent_core": "brahmi_pearls", "negative_keyword_needs": ["free", "home remedy", "side effects"], "original_language": "normalized", "phrase_match_expansion_risk": "low", "product_family": "brahmi_pearls", "product_format": "capsule", "product_variant": null, "query_shape": "brand_product", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": false, "medical_claim_sensitive": false}}</t>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress_and_anxiety", "english_equivalent": "stress and anxiety relief supplements", "landing_page_type": "product_detail", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "jobs"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_relief_supplement", "product_format": "other", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -5814,7 +6626,207 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>brahmi pearls, kerala ayurveda brahmi pearls, brahmi pearls kerala ayurveda</t>
+          <t>stress and anxiety relief supplements, anxiety stress relief supplement, stress anxiety relief supplements</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>fp_0009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "comparison", "ad_group_intent": "competitor", "audience": null, "brand_scope": "competitor", "commercial_intent": "buy", "condition_or_need": "stress_and_anxiety", "english_equivalent": "himalaya stress tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_anxiety_relief", "negative_keyword_needs": ["free", "home remedy", "symptoms", "jobs"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "stress_relief_supplement", "product_format": "tablet", "product_variant": null, "query_shape": "brand_product", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": true, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>himalaya stress tablets</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>fp_0010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "mental stress relief tablets", "landing_page_type": "product_detail", "match_intent_core": "stress_relief_tablet", "negative_keyword_needs": ["free", "home remedy", "home remedies", "prescription"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "ayurvedic_stress_relief_medicine", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>7</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>mental stress tablets, stress management tablets, stress relief ayurvedic tablets, stress relief tablets in ayurveda, stress buster tablet, stress reliever tablet, tablet for tension relief</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>fp_0011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "comparison", "ad_group_intent": "evaluation", "audience": null, "brand_scope": "generic", "commercial_intent": "best", "condition_or_need": "stress", "english_equivalent": "best stress relief tablets", "landing_page_type": "comparison_page", "match_intent_core": "stress_relief_tablet", "negative_keyword_needs": ["free", "home remedy", "home remedies", "prescription"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "ayurvedic_stress_relief_medicine", "product_format": "tablet", "product_variant": null, "query_shape": "product_plus_condition", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>best stress relief tablets</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>fp_0012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "education", "ad_group_intent": "informational", "audience": null, "brand_scope": "generic", "commercial_intent": "informational", "condition_or_need": "stress", "english_equivalent": "sleeping pills for stress relief", "landing_page_type": "educational_page", "match_intent_core": "sleeping_pills_for_stress_relief", "negative_keyword_needs": ["prescription", "psychiatrist", "psychologist", "free"], "original_language": "normalized", "phrase_match_expansion_risk": "high", "product_family": "sleep_aids", "product_format": "tablet", "product_variant": null, "query_shape": "condition_solution", "risk_flags": {"ambiguous_product_mapping": true, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>sleeping pills for stress relief</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>fp_0013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "ayurvedic stress relief medicine", "landing_page_type": "product_detail", "match_intent_core": "ayurvedic_stress_relief_medicine", "negative_keyword_needs": ["free", "home remedy", "home remedies", "prescription"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "ayurvedic_stress_relief_medicine", "product_format": "unknown", "product_variant": null, "query_shape": "product_only", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ayurvedic stress relief medicine</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>fp_0014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "condition", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": "stress", "english_equivalent": "ayurvedic stress relief tablets", "landing_page_type": "condition_page", "match_intent_core": "stress_relief", "negative_keyword_needs": ["home remedy", "free", "symptoms", "causes"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "ayurvedic_stress_medicine", "product_format": "tablet", "product_variant": null, "query_shape": "condition_solution", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": true, "medical_claim_sensitive": true}}</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>4</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>stress free tablets ayurvedic, stress relief medicine in ayurveda, ayurvedic stress tablets, stress tablets ayurvedic</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>fp_0015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": null, "english_equivalent": "brahmi pearls", "landing_page_type": "product_detail", "match_intent_core": "brahmi_pearls", "negative_keyword_needs": ["tablet", "free", "home remedy"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "brahmi", "product_format": "capsule", "product_variant": null, "query_shape": "product_only", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": false, "medical_claim_sensitive": false}}</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>brahmi pearls</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>fp_0016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "efficacy_benefit", "ad_group_intent": "product", "audience": null, "brand_scope": "generic", "commercial_intent": "buy", "condition_or_need": null, "english_equivalent": "brahmi tablets", "landing_page_type": "product_detail", "match_intent_core": "brahmi_tablet", "negative_keyword_needs": ["pearls", "capsule", "free", "home remedy"], "original_language": "normalized", "phrase_match_expansion_risk": "medium", "product_family": "brahmi", "product_format": "tablet", "product_variant": null, "query_shape": "product_only", "risk_flags": {"ambiguous_product_mapping": true, "competitor_term_present": false, "disease_term_present": false, "medical_claim_sensitive": false}}</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>brahmi tablet</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>fp_0017</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "brand_trust", "ad_group_intent": "brand_product", "audience": null, "brand_scope": "brand", "commercial_intent": "buy", "condition_or_need": null, "english_equivalent": "brahmi pearls kerala ayurveda", "landing_page_type": "product_detail", "match_intent_core": "brahmi_pearls", "negative_keyword_needs": ["tablet", "home remedy", "free"], "original_language": "normalized", "phrase_match_expansion_risk": "low", "product_family": "brahmi", "product_format": "capsule", "product_variant": null, "query_shape": "brand_product", "risk_flags": {"ambiguous_product_mapping": false, "competitor_term_present": false, "disease_term_present": false, "medical_claim_sensitive": false}}</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>kerala ayurveda brahmi pearls, brahmi pearls kerala ayurveda</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>fp_0018</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>{"ad_copy_angle": "brand_trust", "ad_group_intent": "brand_product", "audience": null, "brand_scope": "brand", "commercial_intent": "buy", "condition_or_need": null, "english_equivalent": "brahmi tablets kerala ayurveda", "landing_page_type": "product_detail", "match_intent_core": "brahmi_tablet", "negative_keyword_needs": ["pearls", "capsule", "free", "home remedy"], "original_language": "normalized", "phrase_match_expansion_risk": "low", "product_family": "brahmi", "product_format": "tablet", "product_variant": null, "query_shape": "brand_product", "risk_flags": {"ambiguous_product_mapping": true, "competitor_term_present": false, "disease_term_present": false, "medical_claim_sensitive": false}}</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>brahmi tablet kerala ayurveda</t>
         </is>
       </c>
     </row>
